--- a/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-2026-07-15.xlsx
+++ b/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-2026-07-15.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/15 01:02:13</t>
+          <t>07/15 18:54:42</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3478.26</t>
+          <t>2536.23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>af_vip01</t>
+          <t>lao1_vip</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>35000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3478.26</t>
+          <t>2536.23</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3478.26</t>
+          <t>2536.23</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-2026-07-15.xlsx
+++ b/bills/JXZFSP/-5230462985/fc69bc8101c55c7eeca718e92227fbe9b026ec9ec3afcc79a6c130783937e004/bill-2026-07-15.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/15 19:00:42</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2536</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>lao1_vip</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>35000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2536.23</t>
+          <t>35000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2536.23</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2536</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2536.23</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.23</t>
         </is>
       </c>
     </row>
